--- a/artfynd/A 63193-2025 artfynd.xlsx
+++ b/artfynd/A 63193-2025 artfynd.xlsx
@@ -1081,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130755777</v>
+        <v>130755749</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,26 +1092,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1119,10 +1123,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490029</v>
+        <v>490012</v>
       </c>
       <c r="R5" t="n">
-        <v>7013807</v>
+        <v>7013770</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,6 +1161,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på en sälghögstubbe.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1179,22 +1188,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1212,10 +1221,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130755749</v>
+        <v>130755777</v>
       </c>
       <c r="B6" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,30 +1232,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1254,10 +1259,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490012</v>
+        <v>490029</v>
       </c>
       <c r="R6" t="n">
-        <v>7013770</v>
+        <v>7013807</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1292,11 +1297,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Växer på en sälghögstubbe.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130755740</v>
+        <v>130755741</v>
       </c>
       <c r="B7" t="n">
         <v>80317</v>
@@ -1382,11 +1382,7 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1394,10 +1390,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489930</v>
+        <v>490061</v>
       </c>
       <c r="R7" t="n">
-        <v>7013786</v>
+        <v>7013783</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1434,7 +1430,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
+          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1487,10 +1483,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130755770</v>
+        <v>130755752</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,26 +1494,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490124</v>
+        <v>489917</v>
       </c>
       <c r="R8" t="n">
-        <v>7013750</v>
+        <v>7013790</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i gles granskog.</t>
+          <t>På en gammal levande knäckt sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130755752</v>
+        <v>130755773</v>
       </c>
       <c r="B9" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,30 +1634,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1665,10 +1661,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489917</v>
+        <v>490002</v>
       </c>
       <c r="R9" t="n">
-        <v>7013790</v>
+        <v>7013775</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1703,11 +1699,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På en gammal levande knäckt sälg.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1730,22 +1721,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1763,10 +1754,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130755773</v>
+        <v>130755737</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>80317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,21 +1765,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1801,10 +1792,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490002</v>
+        <v>490082</v>
       </c>
       <c r="R10" t="n">
-        <v>7013775</v>
+        <v>7013704</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1839,6 +1830,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växer på en knäckt men levande sälg.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1854,29 +1850,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1894,7 +1885,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130755737</v>
+        <v>130755740</v>
       </c>
       <c r="B11" t="n">
         <v>80317</v>
@@ -1924,7 +1915,11 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1932,10 +1927,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490082</v>
+        <v>489930</v>
       </c>
       <c r="R11" t="n">
-        <v>7013704</v>
+        <v>7013786</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1972,7 +1967,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växer på en knäckt men levande sälg.</t>
+          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2025,10 +2020,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130755741</v>
+        <v>130755770</v>
       </c>
       <c r="B12" t="n">
-        <v>80317</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2036,21 +2031,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2063,10 +2058,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490061</v>
+        <v>490124</v>
       </c>
       <c r="R12" t="n">
-        <v>7013783</v>
+        <v>7013750</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2103,7 +2098,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
+          <t>Långväxta bålar på gran i gles granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2121,24 +2116,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130755735</v>
+        <v>130755759</v>
       </c>
       <c r="B13" t="n">
-        <v>57854</v>
+        <v>91757</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2167,29 +2167,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2199,10 +2198,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489931</v>
+        <v>489903</v>
       </c>
       <c r="R13" t="n">
-        <v>7013444</v>
+        <v>7013683</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2239,7 +2238,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, enstaka några meter upp på en gran.</t>
+          <t>Flertalet slitna gamla fruktkroppar i en stående död gran med full längd i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2248,6 +2247,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130755759</v>
+        <v>130755735</v>
       </c>
       <c r="B14" t="n">
-        <v>91757</v>
+        <v>57854</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2302,28 +2302,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2333,10 +2334,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489903</v>
+        <v>489931</v>
       </c>
       <c r="R14" t="n">
-        <v>7013683</v>
+        <v>7013444</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2373,7 +2374,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flertalet slitna gamla fruktkroppar i en stående död gran med full längd i flerskiktad äldre granskog.</t>
+          <t>Ringhack (savhack), äldre, enstaka några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2382,7 +2383,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2542,7 +2542,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130755780</v>
+        <v>130755772</v>
       </c>
       <c r="B16" t="n">
         <v>79211</v>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489926</v>
+        <v>490096</v>
       </c>
       <c r="R16" t="n">
-        <v>7013704</v>
+        <v>7013750</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2616,6 +2616,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2673,7 +2678,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130755772</v>
+        <v>130755780</v>
       </c>
       <c r="B17" t="n">
         <v>79211</v>
@@ -2711,10 +2716,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490096</v>
+        <v>489926</v>
       </c>
       <c r="R17" t="n">
-        <v>7013750</v>
+        <v>7013704</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2747,11 +2752,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2809,10 +2809,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130755760</v>
+        <v>130755755</v>
       </c>
       <c r="B18" t="n">
-        <v>91781</v>
+        <v>80316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2820,24 +2820,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2847,10 +2851,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489936</v>
+        <v>490062</v>
       </c>
       <c r="R18" t="n">
-        <v>7013555</v>
+        <v>7013785</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2887,7 +2891,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död granstam.</t>
+          <t>Rikligt med bålar på en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2905,29 +2909,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2945,10 +2944,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130755755</v>
+        <v>130755760</v>
       </c>
       <c r="B19" t="n">
-        <v>80316</v>
+        <v>91781</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2956,28 +2955,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2987,10 +2982,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490062</v>
+        <v>489936</v>
       </c>
       <c r="R19" t="n">
-        <v>7013785</v>
+        <v>7013555</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3027,7 +3022,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en skadad levande sälg.</t>
+          <t>Flera fruktkroppar i en stående död granstam.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3045,24 +3040,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130755769</v>
+        <v>130755738</v>
       </c>
       <c r="B20" t="n">
-        <v>79211</v>
+        <v>80317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3091,26 +3091,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3118,10 +3122,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490116</v>
+        <v>489904</v>
       </c>
       <c r="R20" t="n">
-        <v>7013743</v>
+        <v>7013810</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3158,7 +3162,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt och långväxta bålar på en gran i gles granskog.</t>
+          <t>Växer på en levande lutande sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3176,29 +3180,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3216,7 +3215,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130755764</v>
+        <v>130755769</v>
       </c>
       <c r="B21" t="n">
         <v>79211</v>
@@ -3254,10 +3253,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490087</v>
+        <v>490116</v>
       </c>
       <c r="R21" t="n">
-        <v>7013655</v>
+        <v>7013743</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3294,7 +3293,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en stående död delvis avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
+          <t>Rikligt och långväxta bålar på en gran i gles granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3312,6 +3311,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3324,12 +3328,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3347,10 +3351,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130755738</v>
+        <v>130755764</v>
       </c>
       <c r="B22" t="n">
-        <v>80317</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3358,30 +3362,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489904</v>
+        <v>490087</v>
       </c>
       <c r="R22" t="n">
-        <v>7013810</v>
+        <v>7013655</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Växer på en levande lutande sälg.</t>
+          <t>På en stående död delvis avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3449,22 +3449,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -4020,7 +4020,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130755765</v>
+        <v>130755782</v>
       </c>
       <c r="B27" t="n">
         <v>79211</v>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490063</v>
+        <v>489925</v>
       </c>
       <c r="R27" t="n">
-        <v>7013696</v>
+        <v>7013633</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4096,11 +4096,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På död gren av tall.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4113,27 +4108,32 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Dead branch  # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130755731</v>
+        <v>130755765</v>
       </c>
       <c r="B28" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4162,31 +4162,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4194,10 +4189,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489987</v>
+        <v>490063</v>
       </c>
       <c r="R28" t="n">
-        <v>7013746</v>
+        <v>7013696</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4234,7 +4229,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och ytliga, längs några meter på en granstam.</t>
+          <t>På död gren av tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4243,37 +4238,33 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4426,10 +4417,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130755782</v>
+        <v>130755731</v>
       </c>
       <c r="B30" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4437,26 +4428,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4464,10 +4460,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489925</v>
+        <v>489987</v>
       </c>
       <c r="R30" t="n">
-        <v>7013633</v>
+        <v>7013746</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4502,13 +4498,17 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre och ytliga, längs några meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4534,12 +4534,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130755768</v>
+        <v>130755751</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4708,26 +4708,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4735,10 +4739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490119</v>
+        <v>489907</v>
       </c>
       <c r="R32" t="n">
-        <v>7013720</v>
+        <v>7013806</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4775,7 +4779,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i äldre granskog.</t>
+          <t>Rikligt med lunglav på en lutande levande sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4800,22 +4804,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4833,10 +4837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130755751</v>
+        <v>130755730</v>
       </c>
       <c r="B33" t="n">
-        <v>80316</v>
+        <v>91761</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4844,28 +4848,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4875,10 +4879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489907</v>
+        <v>489853</v>
       </c>
       <c r="R33" t="n">
-        <v>7013806</v>
+        <v>7013861</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4913,11 +4917,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en lutande levande sälg.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4933,29 +4932,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4973,10 +4967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130755730</v>
+        <v>130755768</v>
       </c>
       <c r="B34" t="n">
-        <v>91761</v>
+        <v>79211</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4984,30 +4978,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5015,10 +5005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489853</v>
+        <v>490119</v>
       </c>
       <c r="R34" t="n">
-        <v>7013861</v>
+        <v>7013720</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5053,6 +5043,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5068,6 +5063,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130755766</v>
+        <v>130755754</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5114,26 +5114,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5141,10 +5145,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490089</v>
+        <v>489998</v>
       </c>
       <c r="R35" t="n">
-        <v>7013701</v>
+        <v>7013738</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5181,7 +5185,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt med lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5199,24 +5203,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5234,10 +5243,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130755754</v>
+        <v>130755766</v>
       </c>
       <c r="B36" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5245,30 +5254,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5276,10 +5281,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489998</v>
+        <v>490089</v>
       </c>
       <c r="R36" t="n">
-        <v>7013738</v>
+        <v>7013701</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5316,7 +5321,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en gammal sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5334,29 +5339,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130755775</v>
+        <v>130755784</v>
       </c>
       <c r="B38" t="n">
         <v>79211</v>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489948</v>
+        <v>489974</v>
       </c>
       <c r="R38" t="n">
-        <v>7013743</v>
+        <v>7013613</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran intill andra hänglavar i äldre granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5646,7 +5646,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130755784</v>
+        <v>130755775</v>
       </c>
       <c r="B39" t="n">
         <v>79211</v>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489974</v>
+        <v>489948</v>
       </c>
       <c r="R39" t="n">
-        <v>7013613</v>
+        <v>7013743</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gran intill andra hänglavar i äldre granskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5782,10 +5782,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130755748</v>
+        <v>130755776</v>
       </c>
       <c r="B40" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5793,30 +5793,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5824,10 +5820,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490112</v>
+        <v>489982</v>
       </c>
       <c r="R40" t="n">
-        <v>7013757</v>
+        <v>7013779</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5862,11 +5858,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en levande skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5879,27 +5870,32 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6048,10 +6044,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130755776</v>
+        <v>130755748</v>
       </c>
       <c r="B42" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6059,26 +6055,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489982</v>
+        <v>490112</v>
       </c>
       <c r="R42" t="n">
-        <v>7013779</v>
+        <v>7013757</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6124,6 +6124,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på en levande skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6136,32 +6141,27 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>

--- a/artfynd/A 63193-2025 artfynd.xlsx
+++ b/artfynd/A 63193-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130755778</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130755736</v>
+        <v>130755749</v>
       </c>
       <c r="B3" t="n">
-        <v>57854</v>
+        <v>80324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,29 +822,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -854,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490036</v>
+        <v>490012</v>
       </c>
       <c r="R3" t="n">
-        <v>7013472</v>
+        <v>7013770</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, enstaka ytliga ringhack på en gran i barrblandskog.</t>
+          <t>Växer på en sälghögstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,32 +902,38 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -949,7 +954,7 @@
         <v>130755732</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,10 +1086,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130755749</v>
+        <v>130755736</v>
       </c>
       <c r="B5" t="n">
-        <v>80316</v>
+        <v>57862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,28 +1097,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1123,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490012</v>
+        <v>490036</v>
       </c>
       <c r="R5" t="n">
-        <v>7013770</v>
+        <v>7013472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1163,7 +1169,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer på en sälghögstubbe.</t>
+          <t>Ringhack (savhack), äldre, enstaka ytliga ringhack på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,38 +1178,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1224,7 +1224,7 @@
         <v>130755777</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130755741</v>
+        <v>130755770</v>
       </c>
       <c r="B7" t="n">
-        <v>80317</v>
+        <v>79219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490061</v>
+        <v>490124</v>
       </c>
       <c r="R7" t="n">
-        <v>7013783</v>
+        <v>7013750</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
+          <t>Långväxta bålar på gran i gles granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1448,24 +1448,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1483,10 +1488,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130755752</v>
+        <v>130755740</v>
       </c>
       <c r="B8" t="n">
-        <v>80316</v>
+        <v>80325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,21 +1499,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1525,10 +1530,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489917</v>
+        <v>489930</v>
       </c>
       <c r="R8" t="n">
-        <v>7013790</v>
+        <v>7013786</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1565,7 +1570,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en gammal levande knäckt sälg.</t>
+          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,11 +1586,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130755773</v>
+        <v>130755737</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>80325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,21 +1634,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490002</v>
+        <v>490082</v>
       </c>
       <c r="R9" t="n">
-        <v>7013775</v>
+        <v>7013704</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1699,6 +1699,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växer på en knäckt men levande sälg.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1714,29 +1719,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1754,10 +1754,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130755737</v>
+        <v>130755741</v>
       </c>
       <c r="B10" t="n">
-        <v>80317</v>
+        <v>80325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490082</v>
+        <v>490061</v>
       </c>
       <c r="R10" t="n">
-        <v>7013704</v>
+        <v>7013783</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer på en knäckt men levande sälg.</t>
+          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1885,10 +1885,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130755740</v>
+        <v>130755752</v>
       </c>
       <c r="B11" t="n">
-        <v>80317</v>
+        <v>80324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489930</v>
+        <v>489917</v>
       </c>
       <c r="R11" t="n">
-        <v>7013786</v>
+        <v>7013790</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
+          <t>På en gammal levande knäckt sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1983,6 +1983,11 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2020,10 +2025,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130755770</v>
+        <v>130755773</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2058,10 +2063,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490124</v>
+        <v>490002</v>
       </c>
       <c r="R12" t="n">
-        <v>7013750</v>
+        <v>7013775</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2094,11 +2099,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran i gles granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2159,7 +2159,7 @@
         <v>130755759</v>
       </c>
       <c r="B13" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130755735</v>
       </c>
       <c r="B14" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>130755757</v>
       </c>
       <c r="B15" t="n">
-        <v>99291</v>
+        <v>99304</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>130755772</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>130755780</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130755755</v>
+        <v>130755760</v>
       </c>
       <c r="B18" t="n">
-        <v>80316</v>
+        <v>91794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2820,28 +2820,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2851,10 +2847,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490062</v>
+        <v>489936</v>
       </c>
       <c r="R18" t="n">
-        <v>7013785</v>
+        <v>7013555</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2891,7 +2887,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en skadad levande sälg.</t>
+          <t>Flera fruktkroppar i en stående död granstam.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2909,24 +2905,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2944,10 +2945,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130755760</v>
+        <v>130755755</v>
       </c>
       <c r="B19" t="n">
-        <v>91781</v>
+        <v>80324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2955,24 +2956,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2982,10 +2987,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489936</v>
+        <v>490062</v>
       </c>
       <c r="R19" t="n">
-        <v>7013555</v>
+        <v>7013785</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3022,7 +3027,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död granstam.</t>
+          <t>Rikligt med bålar på en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3040,29 +3045,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog.</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130755738</v>
+        <v>130755769</v>
       </c>
       <c r="B20" t="n">
-        <v>80317</v>
+        <v>79219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3091,30 +3091,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3122,10 +3118,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489904</v>
+        <v>490116</v>
       </c>
       <c r="R20" t="n">
-        <v>7013810</v>
+        <v>7013743</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3162,7 +3158,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Växer på en levande lutande sälg.</t>
+          <t>Rikligt och långväxta bålar på en gran i gles granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3180,24 +3176,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3215,10 +3216,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130755769</v>
+        <v>130755764</v>
       </c>
       <c r="B21" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3253,10 +3254,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490116</v>
+        <v>490087</v>
       </c>
       <c r="R21" t="n">
-        <v>7013743</v>
+        <v>7013655</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3293,7 +3294,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt och långväxta bålar på en gran i gles granskog.</t>
+          <t>På en stående död delvis avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3311,11 +3312,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3328,12 +3324,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3351,10 +3347,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130755764</v>
+        <v>130755738</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>80325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3362,26 +3358,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490087</v>
+        <v>489904</v>
       </c>
       <c r="R22" t="n">
-        <v>7013655</v>
+        <v>7013810</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På en stående död delvis avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
+          <t>Växer på en levande lutande sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3449,22 +3449,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
         <v>130755747</v>
       </c>
       <c r="B23" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>130755774</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130755783</v>
+        <v>130755767</v>
       </c>
       <c r="B25" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489944</v>
+        <v>490125</v>
       </c>
       <c r="R25" t="n">
-        <v>7013630</v>
+        <v>7013689</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Bland andra hänglavar på en stående död delvis avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3861,12 +3861,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130755767</v>
+        <v>130755783</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490125</v>
+        <v>489944</v>
       </c>
       <c r="R26" t="n">
-        <v>7013689</v>
+        <v>7013630</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på en stående död delvis avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130755782</v>
+        <v>130755765</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489925</v>
+        <v>490063</v>
       </c>
       <c r="R27" t="n">
-        <v>7013633</v>
+        <v>7013696</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4096,6 +4096,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På död gren av tall.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4108,32 +4113,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130755765</v>
+        <v>130755782</v>
       </c>
       <c r="B28" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490063</v>
+        <v>489925</v>
       </c>
       <c r="R28" t="n">
-        <v>7013696</v>
+        <v>7013633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4227,11 +4227,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På död gren av tall.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4244,27 +4239,32 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Dead branch  # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4285,7 +4285,7 @@
         <v>130755756</v>
       </c>
       <c r="B29" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>130755731</v>
       </c>
       <c r="B30" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>130755733</v>
       </c>
       <c r="B31" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>130755751</v>
       </c>
       <c r="B32" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4837,10 +4837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130755730</v>
+        <v>130755768</v>
       </c>
       <c r="B33" t="n">
-        <v>91761</v>
+        <v>79219</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4848,30 +4848,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4879,10 +4875,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489853</v>
+        <v>490119</v>
       </c>
       <c r="R33" t="n">
-        <v>7013861</v>
+        <v>7013720</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4917,6 +4913,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4932,6 +4933,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ33" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4944,12 +4950,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4967,10 +4973,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130755768</v>
+        <v>130755730</v>
       </c>
       <c r="B34" t="n">
-        <v>79211</v>
+        <v>91774</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4978,26 +4984,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5005,10 +5015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490119</v>
+        <v>489853</v>
       </c>
       <c r="R34" t="n">
-        <v>7013720</v>
+        <v>7013861</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5043,11 +5053,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5063,11 +5068,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130755754</v>
+        <v>130755766</v>
       </c>
       <c r="B35" t="n">
-        <v>80316</v>
+        <v>79219</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5114,30 +5114,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5145,10 +5141,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489998</v>
+        <v>490089</v>
       </c>
       <c r="R35" t="n">
-        <v>7013738</v>
+        <v>7013701</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5185,7 +5181,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en gammal sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5203,29 +5199,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5243,10 +5234,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130755766</v>
+        <v>130755754</v>
       </c>
       <c r="B36" t="n">
-        <v>79211</v>
+        <v>80324</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5254,26 +5245,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5281,10 +5276,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490089</v>
+        <v>489998</v>
       </c>
       <c r="R36" t="n">
-        <v>7013701</v>
+        <v>7013738</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5321,7 +5316,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt med lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5339,24 +5334,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5377,7 +5377,7 @@
         <v>130755779</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130755784</v>
+        <v>130755775</v>
       </c>
       <c r="B38" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489974</v>
+        <v>489948</v>
       </c>
       <c r="R38" t="n">
-        <v>7013613</v>
+        <v>7013743</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gran intill andra hänglavar i äldre granskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5646,10 +5646,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130755775</v>
+        <v>130755784</v>
       </c>
       <c r="B39" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489948</v>
+        <v>489974</v>
       </c>
       <c r="R39" t="n">
-        <v>7013743</v>
+        <v>7013613</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran intill andra hänglavar i äldre granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5785,7 +5785,7 @@
         <v>130755776</v>
       </c>
       <c r="B40" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>130755746</v>
       </c>
       <c r="B41" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>130755748</v>
       </c>
       <c r="B42" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6179,10 +6179,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130755753</v>
+        <v>130755763</v>
       </c>
       <c r="B43" t="n">
-        <v>80316</v>
+        <v>79219</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6190,30 +6190,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6221,10 +6217,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489927</v>
+        <v>490118</v>
       </c>
       <c r="R43" t="n">
-        <v>7013782</v>
+        <v>7013667</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6261,7 +6257,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en tvåstammig sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6279,29 +6275,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6319,10 +6310,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130755763</v>
+        <v>130755753</v>
       </c>
       <c r="B44" t="n">
-        <v>79211</v>
+        <v>80324</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6330,26 +6321,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6357,10 +6352,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490118</v>
+        <v>489927</v>
       </c>
       <c r="R44" t="n">
-        <v>7013667</v>
+        <v>7013782</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6397,7 +6392,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ymnigt med lunglav på en tvåstammig sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6415,24 +6410,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 63193-2025 artfynd.xlsx
+++ b/artfynd/A 63193-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130755778</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130755749</v>
+        <v>130755777</v>
       </c>
       <c r="B3" t="n">
-        <v>80324</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,30 +822,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -853,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490012</v>
+        <v>490029</v>
       </c>
       <c r="R3" t="n">
-        <v>7013770</v>
+        <v>7013807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,11 +887,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer på en sälghögstubbe.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -918,22 +909,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -951,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130755732</v>
+        <v>130755749</v>
       </c>
       <c r="B4" t="n">
-        <v>57862</v>
+        <v>80325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,29 +953,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -994,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489992</v>
+        <v>490012</v>
       </c>
       <c r="R4" t="n">
-        <v>7013750</v>
+        <v>7013770</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1034,7 +1024,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på ca 1 meters höjd på en gran med bitvis avfläckt bark.</t>
+          <t>Växer på en sälghögstubbe.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,6 +1033,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1051,24 +1042,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1086,10 +1082,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130755736</v>
+        <v>130755732</v>
       </c>
       <c r="B5" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1115,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1129,10 +1125,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490036</v>
+        <v>489992</v>
       </c>
       <c r="R5" t="n">
-        <v>7013472</v>
+        <v>7013750</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1169,7 +1165,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, enstaka ytliga ringhack på en gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på ca 1 meters höjd på en gran med bitvis avfläckt bark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,7 +1179,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1221,10 +1217,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130755777</v>
+        <v>130755736</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>57863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,26 +1228,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1259,10 +1260,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490029</v>
+        <v>490036</v>
       </c>
       <c r="R6" t="n">
-        <v>7013807</v>
+        <v>7013472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1297,24 +1298,23 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, enstaka ytliga ringhack på en gran i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130755770</v>
+        <v>130755741</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>80326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490124</v>
+        <v>490061</v>
       </c>
       <c r="R7" t="n">
-        <v>7013750</v>
+        <v>7013783</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i gles granskog.</t>
+          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1448,29 +1448,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1488,10 +1483,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130755740</v>
+        <v>130755773</v>
       </c>
       <c r="B8" t="n">
-        <v>80325</v>
+        <v>79220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1499,30 +1494,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1530,10 +1521,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489930</v>
+        <v>490002</v>
       </c>
       <c r="R8" t="n">
-        <v>7013786</v>
+        <v>7013775</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1568,11 +1559,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1588,24 +1574,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1626,7 +1617,7 @@
         <v>130755737</v>
       </c>
       <c r="B9" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1754,10 +1745,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130755741</v>
+        <v>130755740</v>
       </c>
       <c r="B10" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1784,7 +1775,11 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490061</v>
+        <v>489930</v>
       </c>
       <c r="R10" t="n">
-        <v>7013783</v>
+        <v>7013786</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1832,7 +1827,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
+          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1885,10 +1880,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130755752</v>
+        <v>130755770</v>
       </c>
       <c r="B11" t="n">
-        <v>80324</v>
+        <v>79220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1896,30 +1891,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1927,10 +1918,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489917</v>
+        <v>490124</v>
       </c>
       <c r="R11" t="n">
-        <v>7013790</v>
+        <v>7013750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1967,7 +1958,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en gammal levande knäckt sälg.</t>
+          <t>Långväxta bålar på gran i gles granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1992,22 +1983,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2025,10 +2016,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130755773</v>
+        <v>130755752</v>
       </c>
       <c r="B12" t="n">
-        <v>79219</v>
+        <v>80325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2036,26 +2027,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2063,10 +2058,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490002</v>
+        <v>489917</v>
       </c>
       <c r="R12" t="n">
-        <v>7013775</v>
+        <v>7013790</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2101,6 +2096,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På en gammal levande knäckt sälg.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2123,22 +2123,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130755759</v>
+        <v>130755735</v>
       </c>
       <c r="B13" t="n">
-        <v>91770</v>
+        <v>57863</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2167,28 +2167,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2198,10 +2199,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489903</v>
+        <v>489931</v>
       </c>
       <c r="R13" t="n">
-        <v>7013683</v>
+        <v>7013444</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2238,7 +2239,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flertalet slitna gamla fruktkroppar i en stående död gran med full längd i flerskiktad äldre granskog.</t>
+          <t>Ringhack (savhack), äldre, enstaka några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2247,7 +2248,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130755735</v>
+        <v>130755759</v>
       </c>
       <c r="B14" t="n">
-        <v>57862</v>
+        <v>91771</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2302,29 +2302,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2334,10 +2333,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489931</v>
+        <v>489903</v>
       </c>
       <c r="R14" t="n">
-        <v>7013444</v>
+        <v>7013683</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2374,7 +2373,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, enstaka några meter upp på en gran.</t>
+          <t>Flertalet slitna gamla fruktkroppar i en stående död gran med full längd i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2383,6 +2382,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2429,7 +2429,7 @@
         <v>130755757</v>
       </c>
       <c r="B15" t="n">
-        <v>99304</v>
+        <v>99305</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>130755772</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>130755780</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>130755760</v>
       </c>
       <c r="B18" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>130755755</v>
       </c>
       <c r="B19" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3080,10 +3080,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130755769</v>
+        <v>130755738</v>
       </c>
       <c r="B20" t="n">
-        <v>79219</v>
+        <v>80326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3091,26 +3091,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3118,10 +3122,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490116</v>
+        <v>489904</v>
       </c>
       <c r="R20" t="n">
-        <v>7013743</v>
+        <v>7013810</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3158,7 +3162,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt och långväxta bålar på en gran i gles granskog.</t>
+          <t>Växer på en levande lutande sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3176,29 +3180,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3216,10 +3215,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130755764</v>
+        <v>130755769</v>
       </c>
       <c r="B21" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3254,10 +3253,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490087</v>
+        <v>490116</v>
       </c>
       <c r="R21" t="n">
-        <v>7013655</v>
+        <v>7013743</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3294,7 +3293,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en stående död delvis avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
+          <t>Rikligt och långväxta bålar på en gran i gles granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3312,6 +3311,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3324,12 +3328,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3347,10 +3351,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130755738</v>
+        <v>130755764</v>
       </c>
       <c r="B22" t="n">
-        <v>80325</v>
+        <v>79220</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3358,30 +3362,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489904</v>
+        <v>490087</v>
       </c>
       <c r="R22" t="n">
-        <v>7013810</v>
+        <v>7013655</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Växer på en levande lutande sälg.</t>
+          <t>På en stående död delvis avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3449,22 +3449,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
         <v>130755747</v>
       </c>
       <c r="B23" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>130755774</v>
       </c>
       <c r="B24" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130755767</v>
+        <v>130755783</v>
       </c>
       <c r="B25" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490125</v>
+        <v>489944</v>
       </c>
       <c r="R25" t="n">
-        <v>7013689</v>
+        <v>7013630</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Bland andra hänglavar på en stående död delvis avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3861,12 +3861,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130755783</v>
+        <v>130755767</v>
       </c>
       <c r="B26" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489944</v>
+        <v>490125</v>
       </c>
       <c r="R26" t="n">
-        <v>7013630</v>
+        <v>7013689</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Bland andra hänglavar på en stående död delvis avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130755765</v>
+        <v>130755731</v>
       </c>
       <c r="B27" t="n">
-        <v>79219</v>
+        <v>57863</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4031,26 +4031,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4058,10 +4063,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490063</v>
+        <v>489987</v>
       </c>
       <c r="R27" t="n">
-        <v>7013696</v>
+        <v>7013746</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4098,7 +4103,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På död gren av tall.</t>
+          <t>Ringhack, äldre och ytliga, längs några meter på en granstam.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4107,33 +4112,37 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Dead branch  # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4151,10 +4160,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130755782</v>
+        <v>130755733</v>
       </c>
       <c r="B28" t="n">
-        <v>79219</v>
+        <v>57863</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4162,26 +4171,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4189,10 +4203,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489925</v>
+        <v>489978</v>
       </c>
       <c r="R28" t="n">
-        <v>7013633</v>
+        <v>7013712</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4227,13 +4241,17 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, ytliga längs några meter upp på en granstam med spår av äldre sav/kådaflöde.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4244,7 +4262,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Äödre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4259,12 +4277,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4282,10 +4300,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130755756</v>
+        <v>130755782</v>
       </c>
       <c r="B29" t="n">
-        <v>80324</v>
+        <v>79220</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4293,30 +4311,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4324,10 +4338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489948</v>
+        <v>489925</v>
       </c>
       <c r="R29" t="n">
-        <v>7013625</v>
+        <v>7013633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4362,11 +4376,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4382,24 +4391,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4417,10 +4431,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130755731</v>
+        <v>130755765</v>
       </c>
       <c r="B30" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4428,31 +4442,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4460,10 +4469,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489987</v>
+        <v>490063</v>
       </c>
       <c r="R30" t="n">
-        <v>7013746</v>
+        <v>7013696</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4500,7 +4509,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och ytliga, längs några meter på en granstam.</t>
+          <t>På död gren av tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4509,37 +4518,33 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4557,10 +4562,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130755733</v>
+        <v>130755756</v>
       </c>
       <c r="B31" t="n">
-        <v>57862</v>
+        <v>80325</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4568,29 +4573,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4600,10 +4604,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489978</v>
+        <v>489948</v>
       </c>
       <c r="R31" t="n">
-        <v>7013712</v>
+        <v>7013625</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4640,7 +4644,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, ytliga längs några meter upp på en granstam med spår av äldre sav/kådaflöde.</t>
+          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4649,6 +4653,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4657,29 +4662,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Äödre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130755751</v>
+        <v>130755768</v>
       </c>
       <c r="B32" t="n">
-        <v>80324</v>
+        <v>79220</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4708,30 +4708,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4739,10 +4735,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489907</v>
+        <v>490119</v>
       </c>
       <c r="R32" t="n">
-        <v>7013806</v>
+        <v>7013720</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4779,7 +4775,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en lutande levande sälg.</t>
+          <t>Långväxta bålar på gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4804,22 +4800,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4837,10 +4833,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130755768</v>
+        <v>130755751</v>
       </c>
       <c r="B33" t="n">
-        <v>79219</v>
+        <v>80325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4848,26 +4844,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490119</v>
+        <v>489907</v>
       </c>
       <c r="R33" t="n">
-        <v>7013720</v>
+        <v>7013806</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i äldre granskog.</t>
+          <t>Rikligt med lunglav på en lutande levande sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4940,22 +4940,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4976,7 +4976,7 @@
         <v>130755730</v>
       </c>
       <c r="B34" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>130755766</v>
       </c>
       <c r="B35" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>130755754</v>
       </c>
       <c r="B36" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>130755779</v>
       </c>
       <c r="B37" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>130755775</v>
       </c>
       <c r="B38" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>130755784</v>
       </c>
       <c r="B39" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>130755776</v>
       </c>
       <c r="B40" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>130755746</v>
       </c>
       <c r="B41" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>130755748</v>
       </c>
       <c r="B42" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6179,10 +6179,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130755763</v>
+        <v>130755753</v>
       </c>
       <c r="B43" t="n">
-        <v>79219</v>
+        <v>80325</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6190,26 +6190,30 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6217,10 +6221,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490118</v>
+        <v>489927</v>
       </c>
       <c r="R43" t="n">
-        <v>7013667</v>
+        <v>7013782</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6257,7 +6261,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ymnigt med lunglav på en tvåstammig sälg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6275,24 +6279,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6310,10 +6319,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130755753</v>
+        <v>130755763</v>
       </c>
       <c r="B44" t="n">
-        <v>80324</v>
+        <v>79220</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6321,30 +6330,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6352,10 +6357,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>489927</v>
+        <v>490118</v>
       </c>
       <c r="R44" t="n">
-        <v>7013782</v>
+        <v>7013667</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6392,7 +6397,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en tvåstammig sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6410,29 +6415,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 63193-2025 artfynd.xlsx
+++ b/artfynd/A 63193-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130755778</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>130755777</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>130755749</v>
       </c>
       <c r="B4" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130755732</v>
+        <v>130755736</v>
       </c>
       <c r="B5" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489992</v>
+        <v>490036</v>
       </c>
       <c r="R5" t="n">
-        <v>7013750</v>
+        <v>7013472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på ca 1 meters höjd på en gran med bitvis avfläckt bark.</t>
+          <t>Ringhack (savhack), äldre, enstaka ytliga ringhack på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1217,10 +1217,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130755736</v>
+        <v>130755732</v>
       </c>
       <c r="B6" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490036</v>
+        <v>489992</v>
       </c>
       <c r="R6" t="n">
-        <v>7013472</v>
+        <v>7013750</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, enstaka ytliga ringhack på en gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på ca 1 meters höjd på en gran med bitvis avfläckt bark.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1355,7 +1355,7 @@
         <v>130755741</v>
       </c>
       <c r="B7" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130755773</v>
+        <v>130755737</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>80327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,21 +1494,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490002</v>
+        <v>490082</v>
       </c>
       <c r="R8" t="n">
-        <v>7013775</v>
+        <v>7013704</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1559,6 +1559,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer på en knäckt men levande sälg.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1574,29 +1579,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130755737</v>
+        <v>130755740</v>
       </c>
       <c r="B9" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1644,7 +1644,11 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1652,10 +1656,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490082</v>
+        <v>489930</v>
       </c>
       <c r="R9" t="n">
-        <v>7013704</v>
+        <v>7013786</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1692,7 +1696,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer på en knäckt men levande sälg.</t>
+          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1745,10 +1749,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130755740</v>
+        <v>130755770</v>
       </c>
       <c r="B10" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,30 +1760,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489930</v>
+        <v>490124</v>
       </c>
       <c r="R10" t="n">
-        <v>7013786</v>
+        <v>7013750</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
+          <t>Långväxta bålar på gran i gles granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1845,24 +1845,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1880,10 +1885,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130755770</v>
+        <v>130755752</v>
       </c>
       <c r="B11" t="n">
-        <v>79220</v>
+        <v>80326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1891,26 +1896,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1918,10 +1927,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490124</v>
+        <v>489917</v>
       </c>
       <c r="R11" t="n">
-        <v>7013750</v>
+        <v>7013790</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1958,7 +1967,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i gles granskog.</t>
+          <t>På en gammal levande knäckt sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1983,22 +1992,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2016,10 +2025,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130755752</v>
+        <v>130755773</v>
       </c>
       <c r="B12" t="n">
-        <v>80325</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,30 +2036,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2058,10 +2063,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489917</v>
+        <v>490002</v>
       </c>
       <c r="R12" t="n">
-        <v>7013790</v>
+        <v>7013775</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2096,11 +2101,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På en gammal levande knäckt sälg.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2123,22 +2123,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130755735</v>
+        <v>130755759</v>
       </c>
       <c r="B13" t="n">
-        <v>57863</v>
+        <v>91772</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2167,29 +2167,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2199,10 +2198,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489931</v>
+        <v>489903</v>
       </c>
       <c r="R13" t="n">
-        <v>7013444</v>
+        <v>7013683</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2239,7 +2238,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, enstaka några meter upp på en gran.</t>
+          <t>Flertalet slitna gamla fruktkroppar i en stående död gran med full längd i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2248,6 +2247,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130755759</v>
+        <v>130755735</v>
       </c>
       <c r="B14" t="n">
-        <v>91771</v>
+        <v>57864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2302,28 +2302,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2333,10 +2334,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489903</v>
+        <v>489931</v>
       </c>
       <c r="R14" t="n">
-        <v>7013683</v>
+        <v>7013444</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2373,7 +2374,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flertalet slitna gamla fruktkroppar i en stående död gran med full längd i flerskiktad äldre granskog.</t>
+          <t>Ringhack (savhack), äldre, enstaka några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2382,7 +2383,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2429,7 +2429,7 @@
         <v>130755757</v>
       </c>
       <c r="B15" t="n">
-        <v>99305</v>
+        <v>99308</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130755772</v>
+        <v>130755780</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490096</v>
+        <v>489926</v>
       </c>
       <c r="R16" t="n">
-        <v>7013750</v>
+        <v>7013704</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2616,11 +2616,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2678,10 +2673,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130755780</v>
+        <v>130755772</v>
       </c>
       <c r="B17" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2716,10 +2711,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489926</v>
+        <v>490096</v>
       </c>
       <c r="R17" t="n">
-        <v>7013704</v>
+        <v>7013750</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2752,6 +2747,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2812,7 +2812,7 @@
         <v>130755760</v>
       </c>
       <c r="B18" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>130755755</v>
       </c>
       <c r="B19" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>130755738</v>
       </c>
       <c r="B20" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>130755769</v>
       </c>
       <c r="B21" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>130755764</v>
       </c>
       <c r="B22" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>130755747</v>
       </c>
       <c r="B23" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>130755774</v>
       </c>
       <c r="B24" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>130755783</v>
       </c>
       <c r="B25" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>130755767</v>
       </c>
       <c r="B26" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4020,10 +4020,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130755731</v>
+        <v>130755765</v>
       </c>
       <c r="B27" t="n">
-        <v>57863</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4031,31 +4031,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4063,10 +4058,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489987</v>
+        <v>490063</v>
       </c>
       <c r="R27" t="n">
-        <v>7013746</v>
+        <v>7013696</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4103,7 +4098,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och ytliga, längs några meter på en granstam.</t>
+          <t>På död gren av tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4112,37 +4107,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4160,10 +4151,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130755733</v>
+        <v>130755756</v>
       </c>
       <c r="B28" t="n">
-        <v>57863</v>
+        <v>80326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4171,29 +4162,28 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4203,10 +4193,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489978</v>
+        <v>489948</v>
       </c>
       <c r="R28" t="n">
-        <v>7013712</v>
+        <v>7013625</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4243,7 +4233,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, ytliga längs några meter upp på en granstam med spår av äldre sav/kådaflöde.</t>
+          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4252,6 +4242,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4260,29 +4251,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Äödre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4303,7 +4289,7 @@
         <v>130755782</v>
       </c>
       <c r="B29" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4431,10 +4417,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130755765</v>
+        <v>130755731</v>
       </c>
       <c r="B30" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4442,26 +4428,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4469,10 +4460,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490063</v>
+        <v>489987</v>
       </c>
       <c r="R30" t="n">
-        <v>7013696</v>
+        <v>7013746</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4509,7 +4500,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På död gren av tall.</t>
+          <t>Ringhack, äldre och ytliga, längs några meter på en granstam.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4518,33 +4509,37 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Dead branch  # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4562,10 +4557,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130755756</v>
+        <v>130755733</v>
       </c>
       <c r="B31" t="n">
-        <v>80325</v>
+        <v>57864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4573,28 +4568,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4604,10 +4600,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489948</v>
+        <v>489978</v>
       </c>
       <c r="R31" t="n">
-        <v>7013625</v>
+        <v>7013712</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4644,7 +4640,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
+          <t>Ringhack, äldre, ytliga längs några meter upp på en granstam med spår av äldre sav/kådaflöde.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4653,7 +4649,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4662,24 +4657,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Äödre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130755768</v>
+        <v>130755730</v>
       </c>
       <c r="B32" t="n">
-        <v>79220</v>
+        <v>91776</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4708,26 +4708,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4735,10 +4739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490119</v>
+        <v>489853</v>
       </c>
       <c r="R32" t="n">
-        <v>7013720</v>
+        <v>7013861</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4773,11 +4777,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4793,11 +4792,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ32" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4810,12 +4804,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4833,10 +4827,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130755751</v>
+        <v>130755768</v>
       </c>
       <c r="B33" t="n">
-        <v>80325</v>
+        <v>79221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4844,30 +4838,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4875,10 +4865,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489907</v>
+        <v>490119</v>
       </c>
       <c r="R33" t="n">
-        <v>7013806</v>
+        <v>7013720</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4915,7 +4905,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en lutande levande sälg.</t>
+          <t>Långväxta bålar på gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4940,22 +4930,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4973,10 +4963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130755730</v>
+        <v>130755751</v>
       </c>
       <c r="B34" t="n">
-        <v>91775</v>
+        <v>80326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4984,28 +4974,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -5015,10 +5005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489853</v>
+        <v>489907</v>
       </c>
       <c r="R34" t="n">
-        <v>7013861</v>
+        <v>7013806</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5053,6 +5043,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på en lutande levande sälg.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5068,24 +5063,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5106,7 +5106,7 @@
         <v>130755766</v>
       </c>
       <c r="B35" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>130755754</v>
       </c>
       <c r="B36" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>130755779</v>
       </c>
       <c r="B37" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>130755775</v>
       </c>
       <c r="B38" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>130755784</v>
       </c>
       <c r="B39" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5782,10 +5782,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130755776</v>
+        <v>130755748</v>
       </c>
       <c r="B40" t="n">
-        <v>79220</v>
+        <v>80326</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5793,26 +5793,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5820,10 +5824,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489982</v>
+        <v>490112</v>
       </c>
       <c r="R40" t="n">
-        <v>7013779</v>
+        <v>7013757</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5858,6 +5862,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på en levande skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5870,32 +5879,27 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5916,7 +5920,7 @@
         <v>130755746</v>
       </c>
       <c r="B41" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6044,10 +6048,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130755748</v>
+        <v>130755776</v>
       </c>
       <c r="B42" t="n">
-        <v>80325</v>
+        <v>79221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6055,30 +6059,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490112</v>
+        <v>489982</v>
       </c>
       <c r="R42" t="n">
-        <v>7013757</v>
+        <v>7013779</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6124,11 +6124,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en levande skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6141,27 +6136,32 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
         <v>130755753</v>
       </c>
       <c r="B43" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>130755763</v>
       </c>
       <c r="B44" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 63193-2025 artfynd.xlsx
+++ b/artfynd/A 63193-2025 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130755777</v>
+        <v>130755749</v>
       </c>
       <c r="B3" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,26 +822,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -849,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490029</v>
+        <v>490012</v>
       </c>
       <c r="R3" t="n">
-        <v>7013807</v>
+        <v>7013770</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,6 +891,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer på en sälghögstubbe.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -909,22 +918,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -942,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130755749</v>
+        <v>130755777</v>
       </c>
       <c r="B4" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,30 +962,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -984,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490012</v>
+        <v>490029</v>
       </c>
       <c r="R4" t="n">
-        <v>7013770</v>
+        <v>7013807</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,11 +1027,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växer på en sälghögstubbe.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1049,22 +1049,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130755736</v>
+        <v>130755732</v>
       </c>
       <c r="B5" t="n">
         <v>57864</v>
@@ -1115,7 +1115,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490036</v>
+        <v>489992</v>
       </c>
       <c r="R5" t="n">
-        <v>7013472</v>
+        <v>7013750</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, enstaka ytliga ringhack på en gran i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka på ca 1 meters höjd på en gran med bitvis avfläckt bark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1217,7 +1217,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130755732</v>
+        <v>130755736</v>
       </c>
       <c r="B6" t="n">
         <v>57864</v>
@@ -1250,7 +1250,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489992</v>
+        <v>490036</v>
       </c>
       <c r="R6" t="n">
-        <v>7013750</v>
+        <v>7013472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på ca 1 meters höjd på en gran med bitvis avfläckt bark.</t>
+          <t>Ringhack (savhack), äldre, enstaka ytliga ringhack på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130755741</v>
+        <v>130755770</v>
       </c>
       <c r="B7" t="n">
-        <v>80327</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490061</v>
+        <v>490124</v>
       </c>
       <c r="R7" t="n">
-        <v>7013783</v>
+        <v>7013750</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
+          <t>Långväxta bålar på gran i gles granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1448,24 +1448,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1483,10 +1488,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130755737</v>
+        <v>130755773</v>
       </c>
       <c r="B8" t="n">
-        <v>80327</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,21 +1499,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1521,10 +1526,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490082</v>
+        <v>490002</v>
       </c>
       <c r="R8" t="n">
-        <v>7013704</v>
+        <v>7013775</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1559,11 +1564,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer på en knäckt men levande sälg.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1579,24 +1579,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1614,7 +1619,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130755740</v>
+        <v>130755741</v>
       </c>
       <c r="B9" t="n">
         <v>80327</v>
@@ -1644,11 +1649,7 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1656,10 +1657,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489930</v>
+        <v>490061</v>
       </c>
       <c r="R9" t="n">
-        <v>7013786</v>
+        <v>7013783</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1696,7 +1697,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
+          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1749,10 +1750,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130755770</v>
+        <v>130755737</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>80327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1760,21 +1761,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1787,10 +1788,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490124</v>
+        <v>490082</v>
       </c>
       <c r="R10" t="n">
-        <v>7013750</v>
+        <v>7013704</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1827,7 +1828,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i gles granskog.</t>
+          <t>Växer på en knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1845,29 +1846,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1885,10 +1881,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130755752</v>
+        <v>130755740</v>
       </c>
       <c r="B11" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1896,21 +1892,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1927,10 +1923,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489917</v>
+        <v>489930</v>
       </c>
       <c r="R11" t="n">
-        <v>7013790</v>
+        <v>7013786</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1967,7 +1963,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en gammal levande knäckt sälg.</t>
+          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1983,11 +1979,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2025,10 +2016,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130755773</v>
+        <v>130755752</v>
       </c>
       <c r="B12" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2036,26 +2027,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2063,10 +2058,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490002</v>
+        <v>489917</v>
       </c>
       <c r="R12" t="n">
-        <v>7013775</v>
+        <v>7013790</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2101,6 +2096,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På en gammal levande knäckt sälg.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2123,22 +2123,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130755765</v>
+        <v>130755756</v>
       </c>
       <c r="B27" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4031,26 +4031,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4058,10 +4062,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490063</v>
+        <v>489948</v>
       </c>
       <c r="R27" t="n">
-        <v>7013696</v>
+        <v>7013625</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4098,7 +4102,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På död gren av tall.</t>
+          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4113,27 +4117,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Dead branch  # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4151,10 +4155,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130755756</v>
+        <v>130755765</v>
       </c>
       <c r="B28" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4162,30 +4166,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489948</v>
+        <v>490063</v>
       </c>
       <c r="R28" t="n">
-        <v>7013625</v>
+        <v>7013696</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
+          <t>På död gren av tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4248,27 +4248,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4827,10 +4827,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130755768</v>
+        <v>130755751</v>
       </c>
       <c r="B33" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4838,26 +4838,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4865,10 +4869,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490119</v>
+        <v>489907</v>
       </c>
       <c r="R33" t="n">
-        <v>7013720</v>
+        <v>7013806</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4905,7 +4909,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i äldre granskog.</t>
+          <t>Rikligt med lunglav på en lutande levande sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4930,22 +4934,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4963,10 +4967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130755751</v>
+        <v>130755768</v>
       </c>
       <c r="B34" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4974,30 +4978,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489907</v>
+        <v>490119</v>
       </c>
       <c r="R34" t="n">
-        <v>7013806</v>
+        <v>7013720</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en lutande levande sälg.</t>
+          <t>Långväxta bålar på gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5070,22 +5070,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130755766</v>
+        <v>130755754</v>
       </c>
       <c r="B35" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5114,26 +5114,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5141,10 +5145,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490089</v>
+        <v>489998</v>
       </c>
       <c r="R35" t="n">
-        <v>7013701</v>
+        <v>7013738</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5181,7 +5185,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt med lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5199,24 +5203,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5234,10 +5243,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130755754</v>
+        <v>130755766</v>
       </c>
       <c r="B36" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5245,30 +5254,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5276,10 +5281,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489998</v>
+        <v>490089</v>
       </c>
       <c r="R36" t="n">
-        <v>7013738</v>
+        <v>7013701</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5316,7 +5321,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en gammal sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5334,29 +5339,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5782,7 +5782,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130755748</v>
+        <v>130755746</v>
       </c>
       <c r="B40" t="n">
         <v>80326</v>
@@ -5812,11 +5812,7 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5824,10 +5820,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490112</v>
+        <v>490083</v>
       </c>
       <c r="R40" t="n">
-        <v>7013757</v>
+        <v>7013704</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5864,7 +5860,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en levande skadad sälg.</t>
+          <t>Lunglav som växer på en knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5917,7 +5913,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130755746</v>
+        <v>130755748</v>
       </c>
       <c r="B41" t="n">
         <v>80326</v>
@@ -5947,7 +5943,11 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490083</v>
+        <v>490112</v>
       </c>
       <c r="R41" t="n">
-        <v>7013704</v>
+        <v>7013757</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Lunglav som växer på en knäckt men levande sälg.</t>
+          <t>Rikligt med lunglav på en levande skadad sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 63193-2025 artfynd.xlsx
+++ b/artfynd/A 63193-2025 artfynd.xlsx
@@ -1352,10 +1352,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130755770</v>
+        <v>130755741</v>
       </c>
       <c r="B7" t="n">
-        <v>79221</v>
+        <v>80327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490124</v>
+        <v>490061</v>
       </c>
       <c r="R7" t="n">
-        <v>7013750</v>
+        <v>7013783</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i gles granskog.</t>
+          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1448,29 +1448,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1488,10 +1483,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130755773</v>
+        <v>130755737</v>
       </c>
       <c r="B8" t="n">
-        <v>79221</v>
+        <v>80327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1499,21 +1494,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1526,10 +1521,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490002</v>
+        <v>490082</v>
       </c>
       <c r="R8" t="n">
-        <v>7013775</v>
+        <v>7013704</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,6 +1559,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer på en knäckt men levande sälg.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1579,29 +1579,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1619,7 +1614,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130755741</v>
+        <v>130755740</v>
       </c>
       <c r="B9" t="n">
         <v>80327</v>
@@ -1649,7 +1644,11 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1657,10 +1656,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490061</v>
+        <v>489930</v>
       </c>
       <c r="R9" t="n">
-        <v>7013783</v>
+        <v>7013786</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1697,7 +1696,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
+          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1750,10 +1749,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130755737</v>
+        <v>130755752</v>
       </c>
       <c r="B10" t="n">
-        <v>80327</v>
+        <v>80326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,26 +1760,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1788,10 +1791,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490082</v>
+        <v>489917</v>
       </c>
       <c r="R10" t="n">
-        <v>7013704</v>
+        <v>7013790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1828,7 +1831,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer på en knäckt men levande sälg.</t>
+          <t>På en gammal levande knäckt sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1844,6 +1847,11 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1881,10 +1889,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130755740</v>
+        <v>130755773</v>
       </c>
       <c r="B11" t="n">
-        <v>80327</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1892,30 +1900,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1923,10 +1927,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489930</v>
+        <v>490002</v>
       </c>
       <c r="R11" t="n">
-        <v>7013786</v>
+        <v>7013775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1961,11 +1965,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1981,24 +1980,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2016,10 +2020,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130755752</v>
+        <v>130755770</v>
       </c>
       <c r="B12" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,30 +2031,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489917</v>
+        <v>490124</v>
       </c>
       <c r="R12" t="n">
-        <v>7013790</v>
+        <v>7013750</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en gammal levande knäckt sälg.</t>
+          <t>Långväxta bålar på gran i gles granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2123,22 +2123,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2156,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130755759</v>
+        <v>130755735</v>
       </c>
       <c r="B13" t="n">
-        <v>91772</v>
+        <v>57864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2167,28 +2167,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2198,10 +2199,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489903</v>
+        <v>489931</v>
       </c>
       <c r="R13" t="n">
-        <v>7013683</v>
+        <v>7013444</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2238,7 +2239,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flertalet slitna gamla fruktkroppar i en stående död gran med full längd i flerskiktad äldre granskog.</t>
+          <t>Ringhack (savhack), äldre, enstaka några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2247,7 +2248,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130755735</v>
+        <v>130755759</v>
       </c>
       <c r="B14" t="n">
-        <v>57864</v>
+        <v>91772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2302,29 +2302,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2334,10 +2333,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489931</v>
+        <v>489903</v>
       </c>
       <c r="R14" t="n">
-        <v>7013444</v>
+        <v>7013683</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2374,7 +2373,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, enstaka några meter upp på en gran.</t>
+          <t>Flertalet slitna gamla fruktkroppar i en stående död gran med full längd i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2383,6 +2382,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2542,7 +2542,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130755780</v>
+        <v>130755772</v>
       </c>
       <c r="B16" t="n">
         <v>79221</v>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489926</v>
+        <v>490096</v>
       </c>
       <c r="R16" t="n">
-        <v>7013704</v>
+        <v>7013750</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2616,6 +2616,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2673,7 +2678,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130755772</v>
+        <v>130755780</v>
       </c>
       <c r="B17" t="n">
         <v>79221</v>
@@ -2711,10 +2716,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490096</v>
+        <v>489926</v>
       </c>
       <c r="R17" t="n">
-        <v>7013750</v>
+        <v>7013704</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2747,11 +2752,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -4020,10 +4020,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130755756</v>
+        <v>130755782</v>
       </c>
       <c r="B27" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4031,30 +4031,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4062,10 +4058,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489948</v>
+        <v>489925</v>
       </c>
       <c r="R27" t="n">
-        <v>7013625</v>
+        <v>7013633</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4100,11 +4096,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4120,24 +4111,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4286,10 +4282,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130755782</v>
+        <v>130755756</v>
       </c>
       <c r="B29" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4297,26 +4293,30 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489925</v>
+        <v>489948</v>
       </c>
       <c r="R29" t="n">
-        <v>7013633</v>
+        <v>7013625</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4362,6 +4362,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4377,29 +4382,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130755754</v>
+        <v>130755766</v>
       </c>
       <c r="B35" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5114,30 +5114,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5145,10 +5141,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489998</v>
+        <v>490089</v>
       </c>
       <c r="R35" t="n">
-        <v>7013738</v>
+        <v>7013701</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5185,7 +5181,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en gammal sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5203,29 +5199,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5243,10 +5234,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130755766</v>
+        <v>130755754</v>
       </c>
       <c r="B36" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5254,26 +5245,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5281,10 +5276,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490089</v>
+        <v>489998</v>
       </c>
       <c r="R36" t="n">
-        <v>7013701</v>
+        <v>7013738</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5321,7 +5316,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt med lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5339,24 +5334,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5782,10 +5782,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130755746</v>
+        <v>130755776</v>
       </c>
       <c r="B40" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5793,21 +5793,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490083</v>
+        <v>489982</v>
       </c>
       <c r="R40" t="n">
-        <v>7013704</v>
+        <v>7013779</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5858,11 +5858,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Lunglav som växer på en knäckt men levande sälg.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5875,27 +5870,32 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130755748</v>
+        <v>130755746</v>
       </c>
       <c r="B41" t="n">
         <v>80326</v>
@@ -5943,11 +5943,7 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5955,10 +5951,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490112</v>
+        <v>490083</v>
       </c>
       <c r="R41" t="n">
-        <v>7013757</v>
+        <v>7013704</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5995,7 +5991,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en levande skadad sälg.</t>
+          <t>Lunglav som växer på en knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6048,10 +6044,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130755776</v>
+        <v>130755748</v>
       </c>
       <c r="B42" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6059,26 +6055,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489982</v>
+        <v>490112</v>
       </c>
       <c r="R42" t="n">
-        <v>7013779</v>
+        <v>7013757</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6124,6 +6124,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på en levande skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6136,32 +6141,27 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>

--- a/artfynd/A 63193-2025 artfynd.xlsx
+++ b/artfynd/A 63193-2025 artfynd.xlsx
@@ -2809,10 +2809,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130755760</v>
+        <v>130755755</v>
       </c>
       <c r="B18" t="n">
-        <v>91796</v>
+        <v>80326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2820,24 +2820,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2847,10 +2851,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489936</v>
+        <v>490062</v>
       </c>
       <c r="R18" t="n">
-        <v>7013555</v>
+        <v>7013785</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2887,7 +2891,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död granstam.</t>
+          <t>Rikligt med bålar på en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2905,29 +2909,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2945,10 +2944,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130755755</v>
+        <v>130755760</v>
       </c>
       <c r="B19" t="n">
-        <v>80326</v>
+        <v>91796</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2956,28 +2955,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2987,10 +2982,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490062</v>
+        <v>489936</v>
       </c>
       <c r="R19" t="n">
-        <v>7013785</v>
+        <v>7013555</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3027,7 +3022,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en skadad levande sälg.</t>
+          <t>Flera fruktkroppar i en stående död granstam.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3045,24 +3040,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 63193-2025 artfynd.xlsx
+++ b/artfynd/A 63193-2025 artfynd.xlsx
@@ -2156,10 +2156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130755735</v>
+        <v>130755759</v>
       </c>
       <c r="B13" t="n">
-        <v>57864</v>
+        <v>91772</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2167,29 +2167,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2199,10 +2198,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489931</v>
+        <v>489903</v>
       </c>
       <c r="R13" t="n">
-        <v>7013444</v>
+        <v>7013683</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2239,7 +2238,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, enstaka några meter upp på en gran.</t>
+          <t>Flertalet slitna gamla fruktkroppar i en stående död gran med full längd i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2248,6 +2247,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130755759</v>
+        <v>130755735</v>
       </c>
       <c r="B14" t="n">
-        <v>91772</v>
+        <v>57864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2302,28 +2302,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2333,10 +2334,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489903</v>
+        <v>489931</v>
       </c>
       <c r="R14" t="n">
-        <v>7013683</v>
+        <v>7013444</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2373,7 +2374,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flertalet slitna gamla fruktkroppar i en stående död gran med full längd i flerskiktad äldre granskog.</t>
+          <t>Ringhack (savhack), äldre, enstaka några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2382,7 +2383,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130755755</v>
+        <v>130755760</v>
       </c>
       <c r="B18" t="n">
-        <v>80326</v>
+        <v>91796</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2820,28 +2820,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2851,10 +2847,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490062</v>
+        <v>489936</v>
       </c>
       <c r="R18" t="n">
-        <v>7013785</v>
+        <v>7013555</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2891,7 +2887,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en skadad levande sälg.</t>
+          <t>Flera fruktkroppar i en stående död granstam.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2909,24 +2905,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2944,10 +2945,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130755760</v>
+        <v>130755755</v>
       </c>
       <c r="B19" t="n">
-        <v>91796</v>
+        <v>80326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2955,24 +2956,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2982,10 +2987,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489936</v>
+        <v>490062</v>
       </c>
       <c r="R19" t="n">
-        <v>7013555</v>
+        <v>7013785</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3022,7 +3027,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död granstam.</t>
+          <t>Rikligt med bålar på en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3040,29 +3045,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog.</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 63193-2025 artfynd.xlsx
+++ b/artfynd/A 63193-2025 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130755749</v>
+        <v>130755732</v>
       </c>
       <c r="B3" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,28 +822,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -853,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490012</v>
+        <v>489992</v>
       </c>
       <c r="R3" t="n">
-        <v>7013770</v>
+        <v>7013750</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +894,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer på en sälghögstubbe.</t>
+          <t>Ringhack (savhack), färska, enstaka på ca 1 meters höjd på en gran med bitvis avfläckt bark.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +903,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -911,29 +911,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -951,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130755777</v>
+        <v>130755736</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,26 +957,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490029</v>
+        <v>490036</v>
       </c>
       <c r="R4" t="n">
-        <v>7013807</v>
+        <v>7013472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,24 +1027,23 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, enstaka ytliga ringhack på en gran i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1059,12 +1058,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1082,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130755732</v>
+        <v>130755749</v>
       </c>
       <c r="B5" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,29 +1092,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1125,10 +1123,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489992</v>
+        <v>490012</v>
       </c>
       <c r="R5" t="n">
-        <v>7013750</v>
+        <v>7013770</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,7 +1163,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på ca 1 meters höjd på en gran med bitvis avfläckt bark.</t>
+          <t>Växer på en sälghögstubbe.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,6 +1172,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1182,24 +1181,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1217,10 +1221,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130755736</v>
+        <v>130755777</v>
       </c>
       <c r="B6" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,31 +1232,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1260,10 +1259,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490036</v>
+        <v>490029</v>
       </c>
       <c r="R6" t="n">
-        <v>7013472</v>
+        <v>7013807</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1298,23 +1297,24 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), äldre, enstaka ytliga ringhack på en gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130755741</v>
+        <v>130755740</v>
       </c>
       <c r="B7" t="n">
         <v>80327</v>
@@ -1382,7 +1382,11 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1390,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490061</v>
+        <v>489930</v>
       </c>
       <c r="R7" t="n">
-        <v>7013783</v>
+        <v>7013786</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1430,7 +1434,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
+          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1483,7 +1487,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130755737</v>
+        <v>130755741</v>
       </c>
       <c r="B8" t="n">
         <v>80327</v>
@@ -1521,10 +1525,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490082</v>
+        <v>490061</v>
       </c>
       <c r="R8" t="n">
-        <v>7013704</v>
+        <v>7013783</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1561,7 +1565,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växer på en knäckt men levande sälg.</t>
+          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1614,10 +1618,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130755740</v>
+        <v>130755752</v>
       </c>
       <c r="B9" t="n">
-        <v>80327</v>
+        <v>80326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1625,21 +1629,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1656,10 +1660,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489930</v>
+        <v>489917</v>
       </c>
       <c r="R9" t="n">
-        <v>7013786</v>
+        <v>7013790</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1696,7 +1700,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
+          <t>På en gammal levande knäckt sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1712,6 +1716,11 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1749,10 +1758,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130755752</v>
+        <v>130755773</v>
       </c>
       <c r="B10" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1760,30 +1769,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1791,10 +1796,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489917</v>
+        <v>490002</v>
       </c>
       <c r="R10" t="n">
-        <v>7013790</v>
+        <v>7013775</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1829,11 +1834,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en gammal levande knäckt sälg.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1856,22 +1856,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130755773</v>
+        <v>130755737</v>
       </c>
       <c r="B11" t="n">
-        <v>79221</v>
+        <v>80327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,21 +1900,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490002</v>
+        <v>490082</v>
       </c>
       <c r="R11" t="n">
-        <v>7013775</v>
+        <v>7013704</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1965,6 +1965,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer på en knäckt men levande sälg.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1980,29 +1985,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130755760</v>
+        <v>130755755</v>
       </c>
       <c r="B18" t="n">
-        <v>91796</v>
+        <v>80326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2820,24 +2820,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2847,10 +2851,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489936</v>
+        <v>490062</v>
       </c>
       <c r="R18" t="n">
-        <v>7013555</v>
+        <v>7013785</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2887,7 +2891,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död granstam.</t>
+          <t>Rikligt med bålar på en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2905,29 +2909,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2945,10 +2944,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130755755</v>
+        <v>130755760</v>
       </c>
       <c r="B19" t="n">
-        <v>80326</v>
+        <v>91796</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2956,28 +2955,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2987,10 +2982,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490062</v>
+        <v>489936</v>
       </c>
       <c r="R19" t="n">
-        <v>7013785</v>
+        <v>7013555</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3027,7 +3022,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en skadad levande sälg.</t>
+          <t>Flera fruktkroppar i en stående död granstam.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3045,24 +3040,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130755782</v>
+        <v>130755731</v>
       </c>
       <c r="B27" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4031,26 +4031,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4058,10 +4063,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489925</v>
+        <v>489987</v>
       </c>
       <c r="R27" t="n">
-        <v>7013633</v>
+        <v>7013746</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4096,13 +4101,17 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre och ytliga, längs några meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4128,12 +4137,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4151,10 +4160,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130755765</v>
+        <v>130755733</v>
       </c>
       <c r="B28" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4162,26 +4171,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4189,10 +4203,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490063</v>
+        <v>489978</v>
       </c>
       <c r="R28" t="n">
-        <v>7013696</v>
+        <v>7013712</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4229,7 +4243,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På död gren av tall.</t>
+          <t>Ringhack, äldre, ytliga längs några meter upp på en granstam med spår av äldre sav/kådaflöde.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4238,33 +4252,37 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Äödre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Dead branch  # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4282,10 +4300,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130755756</v>
+        <v>130755782</v>
       </c>
       <c r="B29" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4293,30 +4311,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4324,10 +4338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489948</v>
+        <v>489925</v>
       </c>
       <c r="R29" t="n">
-        <v>7013625</v>
+        <v>7013633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4362,11 +4376,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4382,24 +4391,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4417,10 +4431,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130755731</v>
+        <v>130755765</v>
       </c>
       <c r="B30" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4428,31 +4442,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4460,10 +4469,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489987</v>
+        <v>490063</v>
       </c>
       <c r="R30" t="n">
-        <v>7013746</v>
+        <v>7013696</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4500,7 +4509,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och ytliga, längs några meter på en granstam.</t>
+          <t>På död gren av tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4509,37 +4518,33 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4557,10 +4562,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130755733</v>
+        <v>130755756</v>
       </c>
       <c r="B31" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4568,29 +4573,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4600,10 +4604,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489978</v>
+        <v>489948</v>
       </c>
       <c r="R31" t="n">
-        <v>7013712</v>
+        <v>7013625</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4640,7 +4644,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, ytliga längs några meter upp på en granstam med spår av äldre sav/kådaflöde.</t>
+          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4649,6 +4653,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4657,29 +4662,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Äödre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130755730</v>
+        <v>130755751</v>
       </c>
       <c r="B32" t="n">
-        <v>91776</v>
+        <v>80326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4708,28 +4708,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4739,10 +4739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489853</v>
+        <v>489907</v>
       </c>
       <c r="R32" t="n">
-        <v>7013861</v>
+        <v>7013806</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4777,6 +4777,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på en lutande levande sälg.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4792,24 +4797,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4827,10 +4837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130755751</v>
+        <v>130755768</v>
       </c>
       <c r="B33" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4838,30 +4848,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4869,10 +4875,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489907</v>
+        <v>490119</v>
       </c>
       <c r="R33" t="n">
-        <v>7013806</v>
+        <v>7013720</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4909,7 +4915,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en lutande levande sälg.</t>
+          <t>Långväxta bålar på gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4934,22 +4940,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4967,10 +4973,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130755768</v>
+        <v>130755730</v>
       </c>
       <c r="B34" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4978,26 +4984,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5005,10 +5015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490119</v>
+        <v>489853</v>
       </c>
       <c r="R34" t="n">
-        <v>7013720</v>
+        <v>7013861</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5043,11 +5053,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5063,11 +5068,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 63193-2025 artfynd.xlsx
+++ b/artfynd/A 63193-2025 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130755732</v>
+        <v>130755749</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,29 +822,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -854,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489992</v>
+        <v>490012</v>
       </c>
       <c r="R3" t="n">
-        <v>7013750</v>
+        <v>7013770</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på ca 1 meters höjd på en gran med bitvis avfläckt bark.</t>
+          <t>Växer på en sälghögstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,6 +902,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -911,24 +911,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -946,10 +951,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130755736</v>
+        <v>130755777</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,31 +962,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490036</v>
+        <v>490029</v>
       </c>
       <c r="R4" t="n">
-        <v>7013472</v>
+        <v>7013807</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,23 +1027,24 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), äldre, enstaka ytliga ringhack på en gran i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1058,12 +1059,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1081,10 +1082,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130755749</v>
+        <v>130755736</v>
       </c>
       <c r="B5" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,28 +1093,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1123,10 +1125,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490012</v>
+        <v>490036</v>
       </c>
       <c r="R5" t="n">
-        <v>7013770</v>
+        <v>7013472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1163,7 +1165,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer på en sälghögstubbe.</t>
+          <t>Ringhack (savhack), äldre, enstaka ytliga ringhack på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,38 +1174,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1221,10 +1217,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130755777</v>
+        <v>130755732</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,26 +1228,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1259,10 +1260,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490029</v>
+        <v>489992</v>
       </c>
       <c r="R6" t="n">
-        <v>7013807</v>
+        <v>7013750</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1297,13 +1298,17 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, enstaka på ca 1 meters höjd på en gran med bitvis avfläckt bark.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1312,11 +1317,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130755740</v>
+        <v>130755741</v>
       </c>
       <c r="B7" t="n">
         <v>80327</v>
@@ -1382,11 +1382,7 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1394,10 +1390,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489930</v>
+        <v>490061</v>
       </c>
       <c r="R7" t="n">
-        <v>7013786</v>
+        <v>7013783</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1434,7 +1430,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
+          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1487,7 +1483,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130755741</v>
+        <v>130755737</v>
       </c>
       <c r="B8" t="n">
         <v>80327</v>
@@ -1525,10 +1521,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490061</v>
+        <v>490082</v>
       </c>
       <c r="R8" t="n">
-        <v>7013783</v>
+        <v>7013704</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1565,7 +1561,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
+          <t>Växer på en knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1618,10 +1614,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130755752</v>
+        <v>130755740</v>
       </c>
       <c r="B9" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1629,21 +1625,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1660,10 +1656,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489917</v>
+        <v>489930</v>
       </c>
       <c r="R9" t="n">
-        <v>7013790</v>
+        <v>7013786</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1700,7 +1696,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en gammal levande knäckt sälg.</t>
+          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1716,11 +1712,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1758,10 +1749,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130755773</v>
+        <v>130755752</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,26 +1760,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1796,10 +1791,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490002</v>
+        <v>489917</v>
       </c>
       <c r="R10" t="n">
-        <v>7013775</v>
+        <v>7013790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1834,6 +1829,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en gammal levande knäckt sälg.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1856,22 +1856,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130755737</v>
+        <v>130755773</v>
       </c>
       <c r="B11" t="n">
-        <v>80327</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,21 +1900,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490082</v>
+        <v>490002</v>
       </c>
       <c r="R11" t="n">
-        <v>7013704</v>
+        <v>7013775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1965,11 +1965,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växer på en knäckt men levande sälg.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1985,24 +1980,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2159,7 +2159,7 @@
         <v>130755759</v>
       </c>
       <c r="B13" t="n">
-        <v>91772</v>
+        <v>91780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>130755757</v>
       </c>
       <c r="B15" t="n">
-        <v>99308</v>
+        <v>99322</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>130755760</v>
       </c>
       <c r="B19" t="n">
-        <v>91796</v>
+        <v>91804</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4020,10 +4020,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130755731</v>
+        <v>130755782</v>
       </c>
       <c r="B27" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4031,31 +4031,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4063,10 +4058,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489987</v>
+        <v>489925</v>
       </c>
       <c r="R27" t="n">
-        <v>7013746</v>
+        <v>7013633</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4101,17 +4096,13 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre och ytliga, längs några meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4137,12 +4128,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4160,10 +4151,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130755733</v>
+        <v>130755765</v>
       </c>
       <c r="B28" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4171,31 +4162,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4203,10 +4189,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489978</v>
+        <v>490063</v>
       </c>
       <c r="R28" t="n">
-        <v>7013712</v>
+        <v>7013696</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4243,7 +4229,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, ytliga längs några meter upp på en granstam med spår av äldre sav/kådaflöde.</t>
+          <t>På död gren av tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4252,37 +4238,33 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Äödre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4300,10 +4282,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130755782</v>
+        <v>130755756</v>
       </c>
       <c r="B29" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4311,26 +4293,30 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4338,10 +4324,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489925</v>
+        <v>489948</v>
       </c>
       <c r="R29" t="n">
-        <v>7013633</v>
+        <v>7013625</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4376,6 +4362,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4391,29 +4382,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4431,10 +4417,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130755765</v>
+        <v>130755731</v>
       </c>
       <c r="B30" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4442,26 +4428,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4469,10 +4460,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490063</v>
+        <v>489987</v>
       </c>
       <c r="R30" t="n">
-        <v>7013696</v>
+        <v>7013746</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4509,7 +4500,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På död gren av tall.</t>
+          <t>Ringhack, äldre och ytliga, längs några meter på en granstam.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4518,33 +4509,37 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Dead branch  # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4562,10 +4557,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130755756</v>
+        <v>130755733</v>
       </c>
       <c r="B31" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4573,28 +4568,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4604,10 +4600,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489948</v>
+        <v>489978</v>
       </c>
       <c r="R31" t="n">
-        <v>7013625</v>
+        <v>7013712</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4644,7 +4640,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
+          <t>Ringhack, äldre, ytliga längs några meter upp på en granstam med spår av äldre sav/kådaflöde.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4653,7 +4649,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4662,24 +4657,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Äödre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130755751</v>
+        <v>130755730</v>
       </c>
       <c r="B32" t="n">
-        <v>80326</v>
+        <v>91784</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4708,28 +4708,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4739,10 +4739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489907</v>
+        <v>489853</v>
       </c>
       <c r="R32" t="n">
-        <v>7013806</v>
+        <v>7013861</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4777,11 +4777,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en lutande levande sälg.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4797,29 +4792,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4837,10 +4827,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130755768</v>
+        <v>130755751</v>
       </c>
       <c r="B33" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4848,26 +4838,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4875,10 +4869,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490119</v>
+        <v>489907</v>
       </c>
       <c r="R33" t="n">
-        <v>7013720</v>
+        <v>7013806</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4915,7 +4909,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i äldre granskog.</t>
+          <t>Rikligt med lunglav på en lutande levande sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4940,22 +4934,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4973,10 +4967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130755730</v>
+        <v>130755768</v>
       </c>
       <c r="B34" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4984,30 +4978,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5015,10 +5005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489853</v>
+        <v>490119</v>
       </c>
       <c r="R34" t="n">
-        <v>7013861</v>
+        <v>7013720</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5053,6 +5043,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran i äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5068,6 +5063,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 63193-2025 artfynd.xlsx
+++ b/artfynd/A 63193-2025 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130755749</v>
+        <v>130755777</v>
       </c>
       <c r="B3" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,30 +822,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -853,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490012</v>
+        <v>490029</v>
       </c>
       <c r="R3" t="n">
-        <v>7013770</v>
+        <v>7013807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,11 +887,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer på en sälghögstubbe.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -918,22 +909,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -951,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130755777</v>
+        <v>130755749</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,26 +953,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -989,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490029</v>
+        <v>490012</v>
       </c>
       <c r="R4" t="n">
-        <v>7013807</v>
+        <v>7013770</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,6 +1022,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växer på en sälghögstubbe.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1049,22 +1049,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130755752</v>
+        <v>130755770</v>
       </c>
       <c r="B10" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1760,30 +1760,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1791,10 +1787,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489917</v>
+        <v>490124</v>
       </c>
       <c r="R10" t="n">
-        <v>7013790</v>
+        <v>7013750</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1831,7 +1827,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På en gammal levande knäckt sälg.</t>
+          <t>Långväxta bålar på gran i gles granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1856,22 +1852,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1889,10 +1885,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130755773</v>
+        <v>130755752</v>
       </c>
       <c r="B11" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1900,26 +1896,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490002</v>
+        <v>489917</v>
       </c>
       <c r="R11" t="n">
-        <v>7013775</v>
+        <v>7013790</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1965,6 +1965,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en gammal levande knäckt sälg.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1987,22 +1992,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2020,7 +2025,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130755770</v>
+        <v>130755773</v>
       </c>
       <c r="B12" t="n">
         <v>79221</v>
@@ -2058,10 +2063,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490124</v>
+        <v>490002</v>
       </c>
       <c r="R12" t="n">
-        <v>7013750</v>
+        <v>7013775</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2094,11 +2099,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran i gles granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2429,7 +2429,7 @@
         <v>130755757</v>
       </c>
       <c r="B15" t="n">
-        <v>99322</v>
+        <v>99326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130755772</v>
+        <v>130755780</v>
       </c>
       <c r="B16" t="n">
         <v>79221</v>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490096</v>
+        <v>489926</v>
       </c>
       <c r="R16" t="n">
-        <v>7013750</v>
+        <v>7013704</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2616,11 +2616,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2678,7 +2673,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130755780</v>
+        <v>130755772</v>
       </c>
       <c r="B17" t="n">
         <v>79221</v>
@@ -2716,10 +2711,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489926</v>
+        <v>490096</v>
       </c>
       <c r="R17" t="n">
-        <v>7013704</v>
+        <v>7013750</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2752,6 +2747,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2809,10 +2809,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130755755</v>
+        <v>130755760</v>
       </c>
       <c r="B18" t="n">
-        <v>80326</v>
+        <v>91804</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2820,28 +2820,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2851,10 +2847,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490062</v>
+        <v>489936</v>
       </c>
       <c r="R18" t="n">
-        <v>7013785</v>
+        <v>7013555</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2891,7 +2887,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en skadad levande sälg.</t>
+          <t>Flera fruktkroppar i en stående död granstam.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2909,24 +2905,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2944,10 +2945,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130755760</v>
+        <v>130755755</v>
       </c>
       <c r="B19" t="n">
-        <v>91804</v>
+        <v>80326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2955,24 +2956,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2982,10 +2987,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489936</v>
+        <v>490062</v>
       </c>
       <c r="R19" t="n">
-        <v>7013555</v>
+        <v>7013785</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3022,7 +3027,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död granstam.</t>
+          <t>Rikligt med bålar på en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3040,29 +3045,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog.</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -4020,7 +4020,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130755782</v>
+        <v>130755765</v>
       </c>
       <c r="B27" t="n">
         <v>79221</v>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489925</v>
+        <v>490063</v>
       </c>
       <c r="R27" t="n">
-        <v>7013633</v>
+        <v>7013696</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4096,6 +4096,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På död gren av tall.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4108,32 +4113,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130755765</v>
+        <v>130755756</v>
       </c>
       <c r="B28" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4162,26 +4162,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4189,10 +4193,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490063</v>
+        <v>489948</v>
       </c>
       <c r="R28" t="n">
-        <v>7013696</v>
+        <v>7013625</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4229,7 +4233,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På död gren av tall.</t>
+          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4244,27 +4248,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Dead branch  # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4282,10 +4286,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130755756</v>
+        <v>130755782</v>
       </c>
       <c r="B29" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4293,30 +4297,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489948</v>
+        <v>489925</v>
       </c>
       <c r="R29" t="n">
-        <v>7013625</v>
+        <v>7013633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4362,11 +4362,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4382,24 +4377,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4827,10 +4827,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130755751</v>
+        <v>130755768</v>
       </c>
       <c r="B33" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4838,30 +4838,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4869,10 +4865,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489907</v>
+        <v>490119</v>
       </c>
       <c r="R33" t="n">
-        <v>7013806</v>
+        <v>7013720</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4909,7 +4905,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en lutande levande sälg.</t>
+          <t>Långväxta bålar på gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4934,22 +4930,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4967,10 +4963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130755768</v>
+        <v>130755751</v>
       </c>
       <c r="B34" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4978,26 +4974,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490119</v>
+        <v>489907</v>
       </c>
       <c r="R34" t="n">
-        <v>7013720</v>
+        <v>7013806</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i äldre granskog.</t>
+          <t>Rikligt med lunglav på en lutande levande sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5070,22 +5070,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5782,10 +5782,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130755776</v>
+        <v>130755748</v>
       </c>
       <c r="B40" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5793,26 +5793,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5820,10 +5824,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489982</v>
+        <v>490112</v>
       </c>
       <c r="R40" t="n">
-        <v>7013779</v>
+        <v>7013757</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5858,6 +5862,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på en levande skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5870,32 +5879,27 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6044,10 +6048,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130755748</v>
+        <v>130755776</v>
       </c>
       <c r="B42" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6055,30 +6059,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490112</v>
+        <v>489982</v>
       </c>
       <c r="R42" t="n">
-        <v>7013757</v>
+        <v>7013779</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6124,11 +6124,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en levande skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6141,27 +6136,32 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>

--- a/artfynd/A 63193-2025 artfynd.xlsx
+++ b/artfynd/A 63193-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130755778</v>
+        <v>130755759</v>
       </c>
       <c r="B2" t="n">
-        <v>79243</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490036</v>
+        <v>489903</v>
       </c>
       <c r="R2" t="n">
-        <v>7013703</v>
+        <v>7013683</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog.</t>
+          <t>Flertalet slitna gamla fruktkroppar i en stående död gran med full längd i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,11 +775,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
           <t>gran</t>
@@ -788,12 +787,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130755749</v>
+        <v>130755730</v>
       </c>
       <c r="B3" t="n">
-        <v>80348</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,28 +821,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -853,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490012</v>
+        <v>489853</v>
       </c>
       <c r="R3" t="n">
-        <v>7013770</v>
+        <v>7013861</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,11 +890,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer på en sälghögstubbe.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -911,29 +905,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -951,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130755777</v>
+        <v>130755737</v>
       </c>
       <c r="B4" t="n">
-        <v>79243</v>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -989,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490029</v>
+        <v>490082</v>
       </c>
       <c r="R4" t="n">
-        <v>7013807</v>
+        <v>7013704</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,6 +1016,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växer på en knäckt men levande sälg.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1042,29 +1036,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1082,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130755732</v>
+        <v>130755738</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,29 +1082,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1125,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489992</v>
+        <v>489904</v>
       </c>
       <c r="R5" t="n">
-        <v>7013750</v>
+        <v>7013810</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,7 +1153,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på ca 1 meters höjd på en gran med bitvis avfläckt bark.</t>
+          <t>Växer på en levande lutande sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,6 +1162,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1184,22 +1173,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1217,10 +1206,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130755736</v>
+        <v>130755740</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,29 +1217,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1260,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490036</v>
+        <v>489930</v>
       </c>
       <c r="R6" t="n">
-        <v>7013472</v>
+        <v>7013786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1300,7 +1288,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, enstaka ytliga ringhack på en gran i barrblandskog.</t>
+          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1309,32 +1297,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1352,10 +1341,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130755752</v>
+        <v>130755741</v>
       </c>
       <c r="B7" t="n">
-        <v>80348</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,30 +1352,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1394,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489917</v>
+        <v>490061</v>
       </c>
       <c r="R7" t="n">
-        <v>7013790</v>
+        <v>7013783</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1434,7 +1419,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en gammal levande knäckt sälg.</t>
+          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1450,11 +1435,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1492,14 +1472,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130755773</v>
+        <v>130755763</v>
       </c>
       <c r="B8" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1530,10 +1510,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490002</v>
+        <v>490118</v>
       </c>
       <c r="R8" t="n">
-        <v>7013775</v>
+        <v>7013667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1568,6 +1548,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1581,11 +1566,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1623,14 +1603,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130755770</v>
+        <v>130755764</v>
       </c>
       <c r="B9" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1661,10 +1641,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490124</v>
+        <v>490087</v>
       </c>
       <c r="R9" t="n">
-        <v>7013750</v>
+        <v>7013655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1701,7 +1681,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i gles granskog.</t>
+          <t>På en stående död delvis avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1719,11 +1699,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1736,12 +1711,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1759,32 +1734,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130755741</v>
+        <v>130755765</v>
       </c>
       <c r="B10" t="n">
-        <v>80349</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1797,10 +1772,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490061</v>
+        <v>490063</v>
       </c>
       <c r="R10" t="n">
-        <v>7013783</v>
+        <v>7013696</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1837,7 +1812,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Intill lunglav på en skadad levande sälg i äldre granskog.</t>
+          <t>På död gren av tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1852,27 +1827,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1890,32 +1865,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130755737</v>
+        <v>130755766</v>
       </c>
       <c r="B11" t="n">
-        <v>80349</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1928,10 +1903,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490082</v>
+        <v>490089</v>
       </c>
       <c r="R11" t="n">
-        <v>7013704</v>
+        <v>7013701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1968,7 +1943,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växer på en knäckt men levande sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1988,22 +1963,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2021,41 +1996,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130755740</v>
+        <v>130755767</v>
       </c>
       <c r="B12" t="n">
-        <v>80349</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2063,10 +2034,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489930</v>
+        <v>490125</v>
       </c>
       <c r="R12" t="n">
-        <v>7013786</v>
+        <v>7013689</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2103,7 +2074,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Skrovellav på en tvåstammig sälg intill lunglav.</t>
+          <t>Bland andra hänglavar på en stående död delvis avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2121,24 +2092,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2156,41 +2132,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130755759</v>
+        <v>130755768</v>
       </c>
       <c r="B13" t="n">
-        <v>91804</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2198,10 +2170,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489903</v>
+        <v>490119</v>
       </c>
       <c r="R13" t="n">
-        <v>7013683</v>
+        <v>7013720</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2238,7 +2210,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flertalet slitna gamla fruktkroppar i en stående död gran med full längd i flerskiktad äldre granskog.</t>
+          <t>Långväxta bålar på gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2256,6 +2228,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2268,12 +2245,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2291,42 +2268,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130755735</v>
+        <v>130755769</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2334,10 +2306,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489931</v>
+        <v>490116</v>
       </c>
       <c r="R14" t="n">
-        <v>7013444</v>
+        <v>7013743</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2374,7 +2346,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, enstaka några meter upp på en gran.</t>
+          <t>Rikligt och långväxta bålar på en gran i gles granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2383,6 +2355,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2391,6 +2364,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ14" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2403,12 +2381,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2426,42 +2404,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130755757</v>
+        <v>130755770</v>
       </c>
       <c r="B15" t="n">
-        <v>99350</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2469,10 +2442,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489938</v>
+        <v>490124</v>
       </c>
       <c r="R15" t="n">
-        <v>7013520</v>
+        <v>7013750</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2507,6 +2480,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran i gles granskog.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2524,7 +2502,27 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre grandominerad skog.</t>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2545,11 +2543,11 @@
         <v>130755772</v>
       </c>
       <c r="B16" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2678,14 +2676,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130755780</v>
+        <v>130755773</v>
       </c>
       <c r="B17" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2716,10 +2714,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489926</v>
+        <v>490002</v>
       </c>
       <c r="R17" t="n">
-        <v>7013704</v>
+        <v>7013775</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2809,41 +2807,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130755755</v>
+        <v>130755774</v>
       </c>
       <c r="B18" t="n">
-        <v>80348</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2851,10 +2845,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490062</v>
+        <v>489964</v>
       </c>
       <c r="R18" t="n">
-        <v>7013785</v>
+        <v>7013717</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2889,11 +2883,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar på en skadad levande sälg.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2909,24 +2898,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2944,37 +2938,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130755760</v>
+        <v>130755775</v>
       </c>
       <c r="B19" t="n">
-        <v>91828</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2982,10 +2976,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489936</v>
+        <v>489948</v>
       </c>
       <c r="R19" t="n">
-        <v>7013555</v>
+        <v>7013743</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3022,7 +3016,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död granstam.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3042,7 +3036,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Flerskiktad äldre granskog.</t>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3057,12 +3051,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3080,14 +3074,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130755764</v>
+        <v>130755776</v>
       </c>
       <c r="B20" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -3118,10 +3112,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490087</v>
+        <v>489982</v>
       </c>
       <c r="R20" t="n">
-        <v>7013655</v>
+        <v>7013779</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3156,11 +3150,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På en stående död delvis avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3176,6 +3165,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3188,12 +3182,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3211,14 +3205,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130755769</v>
+        <v>130755777</v>
       </c>
       <c r="B21" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3249,10 +3243,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490116</v>
+        <v>490029</v>
       </c>
       <c r="R21" t="n">
-        <v>7013743</v>
+        <v>7013807</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3285,11 +3279,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt och långväxta bålar på en gran i gles granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3347,41 +3336,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130755738</v>
+        <v>130755778</v>
       </c>
       <c r="B22" t="n">
-        <v>80349</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3389,10 +3374,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489904</v>
+        <v>490036</v>
       </c>
       <c r="R22" t="n">
-        <v>7013810</v>
+        <v>7013703</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3429,7 +3414,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Växer på en levande lutande sälg.</t>
+          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3447,24 +3432,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3482,41 +3472,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130755747</v>
+        <v>130755779</v>
       </c>
       <c r="B23" t="n">
-        <v>80348</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3524,10 +3510,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490114</v>
+        <v>489969</v>
       </c>
       <c r="R23" t="n">
-        <v>7013685</v>
+        <v>7013710</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3564,7 +3550,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en grov gammal sälg i barrblandskog.</t>
+          <t>Växer på en klen undertryckt död gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3579,27 +3565,32 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3617,14 +3608,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130755767</v>
+        <v>130755780</v>
       </c>
       <c r="B24" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3655,10 +3646,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490125</v>
+        <v>489926</v>
       </c>
       <c r="R24" t="n">
-        <v>7013689</v>
+        <v>7013704</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3693,11 +3684,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bland andra hänglavar på en stående död delvis avbarkad gran med full längd och potentiella födosökspår av tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3730,12 +3716,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3753,14 +3739,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130755774</v>
+        <v>130755782</v>
       </c>
       <c r="B25" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3791,10 +3777,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489964</v>
+        <v>489925</v>
       </c>
       <c r="R25" t="n">
-        <v>7013717</v>
+        <v>7013633</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3887,11 +3873,11 @@
         <v>130755783</v>
       </c>
       <c r="B26" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -4020,14 +4006,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130755782</v>
+        <v>130755784</v>
       </c>
       <c r="B27" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -4058,10 +4044,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489925</v>
+        <v>489974</v>
       </c>
       <c r="R27" t="n">
-        <v>7013633</v>
+        <v>7013613</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4094,6 +4080,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran intill andra hänglavar i äldre granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4151,10 +4142,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130755765</v>
+        <v>130755746</v>
       </c>
       <c r="B28" t="n">
-        <v>79243</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4162,21 +4153,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4189,10 +4180,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490063</v>
+        <v>490083</v>
       </c>
       <c r="R28" t="n">
-        <v>7013696</v>
+        <v>7013704</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4229,7 +4220,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På död gren av tall.</t>
+          <t>Lunglav som växer på en knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4249,22 +4240,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Dead branch  # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4282,10 +4273,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130755756</v>
+        <v>130755747</v>
       </c>
       <c r="B29" t="n">
-        <v>80348</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4324,10 +4315,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489948</v>
+        <v>490114</v>
       </c>
       <c r="R29" t="n">
-        <v>7013625</v>
+        <v>7013685</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4364,7 +4355,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
+          <t>Ymnigt med lunglav på en grov gammal sälg i barrblandskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4379,7 +4370,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4417,10 +4408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130755731</v>
+        <v>130755748</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4428,29 +4419,28 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4460,10 +4450,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489987</v>
+        <v>490112</v>
       </c>
       <c r="R30" t="n">
-        <v>7013746</v>
+        <v>7013757</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4500,7 +4490,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och ytliga, längs några meter på en granstam.</t>
+          <t>Rikligt med lunglav på en levande skadad sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4509,37 +4499,33 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4557,10 +4543,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130755733</v>
+        <v>130755749</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4568,29 +4554,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4600,10 +4585,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489978</v>
+        <v>490012</v>
       </c>
       <c r="R31" t="n">
-        <v>7013712</v>
+        <v>7013770</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4640,7 +4625,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, ytliga längs några meter upp på en granstam med spår av äldre sav/kådaflöde.</t>
+          <t>Växer på en sälghögstubbe.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4649,6 +4634,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4659,27 +4645,27 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Äödre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4697,10 +4683,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130755751</v>
+        <v>130755750</v>
       </c>
       <c r="B32" t="n">
-        <v>80348</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4739,10 +4725,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489907</v>
+        <v>489901</v>
       </c>
       <c r="R32" t="n">
-        <v>7013806</v>
+        <v>7013822</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4779,7 +4765,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en lutande levande sälg.</t>
+          <t>Rikligt med lunglav på en sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4837,10 +4823,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130755768</v>
+        <v>130755751</v>
       </c>
       <c r="B33" t="n">
-        <v>79243</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4848,26 +4834,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4875,10 +4865,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490119</v>
+        <v>489907</v>
       </c>
       <c r="R33" t="n">
-        <v>7013720</v>
+        <v>7013806</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4915,7 +4905,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i äldre granskog.</t>
+          <t>Rikligt med lunglav på en lutande levande sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4940,22 +4930,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4973,10 +4963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130755730</v>
+        <v>130755752</v>
       </c>
       <c r="B34" t="n">
-        <v>91808</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4984,28 +4974,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -5015,10 +5005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489853</v>
+        <v>489917</v>
       </c>
       <c r="R34" t="n">
-        <v>7013861</v>
+        <v>7013790</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5053,6 +5043,11 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På en gammal levande knäckt sälg.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -5068,24 +5063,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130755766</v>
+        <v>130755753</v>
       </c>
       <c r="B35" t="n">
-        <v>79243</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5114,26 +5114,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5141,10 +5145,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490089</v>
+        <v>489927</v>
       </c>
       <c r="R35" t="n">
-        <v>7013701</v>
+        <v>7013782</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5181,7 +5185,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ymnigt med lunglav på en tvåstammig sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5199,24 +5203,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+        </is>
+      </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5237,7 +5246,7 @@
         <v>130755754</v>
       </c>
       <c r="B36" t="n">
-        <v>80348</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5374,10 +5383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130755779</v>
+        <v>130755755</v>
       </c>
       <c r="B37" t="n">
-        <v>79243</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5385,26 +5394,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5412,10 +5425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489969</v>
+        <v>490062</v>
       </c>
       <c r="R37" t="n">
-        <v>7013710</v>
+        <v>7013785</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5452,7 +5465,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Växer på en klen undertryckt död gran i äldre granskog.</t>
+          <t>Rikligt med bålar på en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5470,29 +5483,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5510,10 +5518,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130755775</v>
+        <v>130755756</v>
       </c>
       <c r="B38" t="n">
-        <v>79243</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5521,26 +5529,30 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5551,7 +5563,7 @@
         <v>489948</v>
       </c>
       <c r="R38" t="n">
-        <v>7013743</v>
+        <v>7013625</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5588,7 +5600,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Lunglav med uttorkade bålar på en tvåstammig skadad levande sälg vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5606,29 +5618,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5646,10 +5653,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130755784</v>
+        <v>130755731</v>
       </c>
       <c r="B39" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5657,26 +5664,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5684,10 +5696,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>489974</v>
+        <v>489987</v>
       </c>
       <c r="R39" t="n">
-        <v>7013613</v>
+        <v>7013746</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5724,7 +5736,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gran intill andra hänglavar i äldre granskog.</t>
+          <t>Ringhack, äldre och ytliga, längs några meter på en granstam.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5733,7 +5745,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5759,12 +5770,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5782,10 +5793,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130755776</v>
+        <v>130755732</v>
       </c>
       <c r="B40" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5793,26 +5804,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5820,10 +5836,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489982</v>
+        <v>489992</v>
       </c>
       <c r="R40" t="n">
-        <v>7013779</v>
+        <v>7013750</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5858,13 +5874,17 @@
           <t>2026-01-15</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, enstaka på ca 1 meters höjd på en gran med bitvis avfläckt bark.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5873,11 +5893,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
-        </is>
-      </c>
       <c r="AJ40" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5890,12 +5905,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5913,10 +5928,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130755746</v>
+        <v>130755733</v>
       </c>
       <c r="B41" t="n">
-        <v>80348</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5924,26 +5939,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5951,10 +5971,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490083</v>
+        <v>489978</v>
       </c>
       <c r="R41" t="n">
-        <v>7013704</v>
+        <v>7013712</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5991,7 +6011,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Lunglav som växer på en knäckt men levande sälg.</t>
+          <t>Ringhack, äldre, ytliga längs några meter upp på en granstam med spår av äldre sav/kådaflöde.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6000,33 +6020,37 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Äödre grandominerad skog med inslag av björk, tall och sälg.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6044,10 +6068,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130755748</v>
+        <v>130755735</v>
       </c>
       <c r="B42" t="n">
-        <v>80348</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6055,28 +6079,29 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -6086,10 +6111,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490112</v>
+        <v>489931</v>
       </c>
       <c r="R42" t="n">
-        <v>7013757</v>
+        <v>7013444</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6126,7 +6151,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en levande skadad sälg.</t>
+          <t>Ringhack (savhack), äldre, enstaka några meter upp på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6135,33 +6160,32 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6179,10 +6203,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130755753</v>
+        <v>130755736</v>
       </c>
       <c r="B43" t="n">
-        <v>80348</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6190,28 +6214,29 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6221,10 +6246,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489927</v>
+        <v>490036</v>
       </c>
       <c r="R43" t="n">
-        <v>7013782</v>
+        <v>7013472</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6261,7 +6286,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav på en tvåstammig sälg.</t>
+          <t>Ringhack (savhack), äldre, enstaka ytliga ringhack på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6270,38 +6295,32 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Äldre grandominerad skog med inslag av björk, tall och sälg.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6319,37 +6338,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130755763</v>
+        <v>130755757</v>
       </c>
       <c r="B44" t="n">
-        <v>79243</v>
+        <v>99456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6357,10 +6381,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490118</v>
+        <v>489938</v>
       </c>
       <c r="R44" t="n">
-        <v>7013667</v>
+        <v>7013520</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6395,11 +6419,6 @@
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6415,24 +6434,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 63193-2025 artfynd.xlsx
+++ b/artfynd/A 63193-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755759</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -937,6 +947,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755730</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1068,6 +1083,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755737</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1203,6 +1223,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755738</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1338,6 +1363,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755740</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1469,6 +1499,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755741</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1600,6 +1635,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755763</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1731,6 +1771,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755764</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1862,6 +1907,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755765</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1993,6 +2043,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755766</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2129,6 +2184,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755767</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2265,6 +2325,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755768</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2401,6 +2466,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755769</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2537,6 +2607,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755770</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2673,6 +2748,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755772</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2804,6 +2884,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755773</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2935,6 +3020,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755774</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3071,6 +3161,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755775</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3202,6 +3297,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755776</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3333,6 +3433,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755777</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3469,6 +3574,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755778</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3605,6 +3715,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755779</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3736,6 +3851,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755780</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3867,6 +3987,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755782</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4003,6 +4128,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755783</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4139,6 +4269,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755784</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4270,6 +4405,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755746</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4405,6 +4545,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755747</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4540,6 +4685,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755748</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4680,6 +4830,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755749</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4820,6 +4975,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755750</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4960,6 +5120,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755751</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5100,6 +5265,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755752</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5240,6 +5410,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755753</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5380,6 +5555,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755754</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5515,6 +5695,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755755</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5650,6 +5835,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755756</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5790,6 +5980,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755731</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5925,6 +6120,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755732</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6065,6 +6265,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755733</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6200,6 +6405,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755735</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6335,6 +6545,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755736</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6451,8 +6666,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755757</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>